--- a/translations/15.7.0/ship_diff.xlsx
+++ b/translations/15.7.0/ship_diff.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="舰船差异" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="舰船差异" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'舰船差异'!$A$1:$I$21</definedName>
@@ -521,7 +521,11 @@
           <t>Conqueror CLR</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>征服者 CLR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -552,7 +556,11 @@
           <t>Conqueror CLR</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>征服者 CLR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -583,7 +591,11 @@
           <t>Latouche-Tréville</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>拉图什-特雷维尔</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -614,7 +626,11 @@
           <t>Latouche-Tréville</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>拉图什-特雷维尔</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -645,7 +661,11 @@
           <t>Ph. van Almonde</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>菲利普·范·阿尔蒙德</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -676,7 +696,11 @@
           <t>Philips van Almonde</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>菲利普·范·阿尔蒙德</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -719,7 +743,11 @@
           <t>Montecuccoli</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>蒙泰库科利</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -762,7 +790,11 @@
           <t>Raimondo Montecuccoli</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>莱蒙多‧蒙泰库科利</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -793,7 +825,11 @@
           <t>La Spezia</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>拉斯佩齐亚</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -824,7 +860,11 @@
           <t>La Spezia</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>拉斯佩齐亚</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -855,7 +895,11 @@
           <t>Tōgasa</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>远笠</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -886,7 +930,11 @@
           <t>Tōgasa</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>远笠</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -917,7 +965,11 @@
           <t>Respublika</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>共和国</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -948,7 +1000,11 @@
           <t>Respublika</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>共和国</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -979,7 +1035,11 @@
           <t>Sov. Rossiya</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>苏维埃俄罗斯</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1010,7 +1070,11 @@
           <t>Sovetskaya Rossiya</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>苏维埃俄罗斯</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1053,7 +1117,11 @@
           <t>Cuauhtémoc</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>夸乌特莫克</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1096,7 +1164,11 @@
           <t>Cuauhtémoc</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>夸乌特莫克</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1139,7 +1211,11 @@
           <t>Heracles</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>赫拉克勒斯</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1182,7 +1258,11 @@
           <t>Heracles</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>赫拉克勒斯</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I21"/>

--- a/translations/15.7.0/ship_diff.xlsx
+++ b/translations/15.7.0/ship_diff.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,7 +33,11 @@
       <color rgb="FFFFFFFF"/>
     </font>
     <font>
-      <name val="Consolas"/>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -62,10 +66,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,19 +503,19 @@
           <t>IDS_PBSB920</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>征服者 炫彩</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>征服者CLR</t>
         </is>
@@ -521,11 +526,7 @@
           <t>Conqueror CLR</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>征服者 CLR</t>
-        </is>
-      </c>
+      <c r="I2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -533,19 +534,19 @@
           <t>IDS_PBSB920_FULL</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>征服者 炫彩</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>征服者CLR</t>
         </is>
@@ -556,11 +557,7 @@
           <t>Conqueror CLR</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>征服者 CLR</t>
-        </is>
-      </c>
+      <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -568,19 +565,19 @@
           <t>IDS_PFSC720</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>拉图什-特雷维尔</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>拉图什·特雷维尔</t>
         </is>
@@ -591,11 +588,7 @@
           <t>Latouche-Tréville</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>拉图什-特雷维尔</t>
-        </is>
-      </c>
+      <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -603,19 +596,19 @@
           <t>IDS_PFSC720_FULL</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>拉图什-特雷维尔</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>拉图什·特雷维尔</t>
         </is>
@@ -626,11 +619,7 @@
           <t>Latouche-Tréville</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>拉图什-特雷维尔</t>
-        </is>
-      </c>
+      <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -638,19 +627,19 @@
           <t>IDS_PHSD708</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>菲利普·范·阿尔蒙德</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>菲利普·范·阿尔蒙德</t>
         </is>
@@ -661,11 +650,7 @@
           <t>Ph. van Almonde</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>菲利普·范·阿尔蒙德</t>
-        </is>
-      </c>
+      <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -673,19 +658,19 @@
           <t>IDS_PHSD708_FULL</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>菲利普·范·阿尔蒙德</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>菲利普·范·阿尔蒙德</t>
         </is>
@@ -696,11 +681,7 @@
           <t>Philips van Almonde</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>菲利普·范·阿尔蒙德</t>
-        </is>
-      </c>
+      <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -708,27 +689,27 @@
           <t>IDS_PISC105</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>修改</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>蒙德库克利</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>蒙泰库科利</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>莱蒙多•蒙德库克利</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>莱蒙多•蒙德库克利</t>
         </is>
@@ -743,11 +724,7 @@
           <t>Montecuccoli</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>蒙泰库科利</t>
-        </is>
-      </c>
+      <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -755,27 +732,27 @@
           <t>IDS_PISC105_FULL</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>修改</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>莱蒙多·蒙德库克利</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>莱蒙多‧蒙泰库科利</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>莱蒙多•蒙德库克利</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>莱蒙多•蒙德库克利</t>
         </is>
@@ -790,11 +767,7 @@
           <t>Raimondo Montecuccoli</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>莱蒙多‧蒙泰库科利</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -802,19 +775,19 @@
           <t>IDS_PISC739</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>拉斯佩齐亚</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>拉斯佩齐亚</t>
         </is>
@@ -825,11 +798,7 @@
           <t>La Spezia</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>拉斯佩齐亚</t>
-        </is>
-      </c>
+      <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -837,19 +806,19 @@
           <t>IDS_PISC739_FULL</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>拉斯佩齐亚</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>拉斯佩齐亚</t>
         </is>
@@ -860,11 +829,7 @@
           <t>La Spezia</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>拉斯佩齐亚</t>
-        </is>
-      </c>
+      <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -872,19 +837,19 @@
           <t>IDS_PJSB730</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>鳝</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>远笠</t>
         </is>
@@ -895,11 +860,7 @@
           <t>Tōgasa</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>远笠</t>
-        </is>
-      </c>
+      <c r="I12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -907,19 +868,19 @@
           <t>IDS_PJSB730_FULL</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>鳝</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>远笠</t>
         </is>
@@ -930,11 +891,7 @@
           <t>Tōgasa</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>远笠</t>
-        </is>
-      </c>
+      <c r="I13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -942,19 +899,19 @@
           <t>IDS_PRSB729</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>共和国</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>共和</t>
         </is>
@@ -965,11 +922,7 @@
           <t>Respublika</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>共和国</t>
-        </is>
-      </c>
+      <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -977,19 +930,19 @@
           <t>IDS_PRSB729_FULL</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>共和国</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>共和</t>
         </is>
@@ -1000,11 +953,7 @@
           <t>Respublika</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>共和国</t>
-        </is>
-      </c>
+      <c r="I15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1012,19 +961,19 @@
           <t>IDS_PRSB739</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>苏维埃罗西亚</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>苏维埃罗西亚</t>
         </is>
@@ -1035,11 +984,7 @@
           <t>Sov. Rossiya</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>苏维埃俄罗斯</t>
-        </is>
-      </c>
+      <c r="I16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1047,19 +992,19 @@
           <t>IDS_PRSB739_FULL</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>苏维埃罗西亚</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>苏维埃罗西亚</t>
         </is>
@@ -1070,11 +1015,7 @@
           <t>Sovetskaya Rossiya</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>苏维埃俄罗斯</t>
-        </is>
-      </c>
+      <c r="I17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1082,27 +1023,27 @@
           <t>IDS_PVSD018</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>修改</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>瓜特穆斯</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>夸乌特莫克</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>瓜特穆斯</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>瓜特穆斯</t>
         </is>
@@ -1117,11 +1058,7 @@
           <t>Cuauhtémoc</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>夸乌特莫克</t>
-        </is>
-      </c>
+      <c r="I18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1129,27 +1066,27 @@
           <t>IDS_PVSD018_FULL</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>修改</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>瓜特穆斯</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>夸乌特莫克</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>瓜特穆斯</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>瓜特穆斯</t>
         </is>
@@ -1164,11 +1101,7 @@
           <t>Cuauhtémoc</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>夸乌特莫克</t>
-        </is>
-      </c>
+      <c r="I19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1176,27 +1109,27 @@
           <t>IDS_PXSB103</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>修改</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">赫拉克勒斯 </t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">赫拉克勒斯 </t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Heracles</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Heracles</t>
         </is>
@@ -1211,11 +1144,7 @@
           <t>Heracles</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>赫拉克勒斯</t>
-        </is>
-      </c>
+      <c r="I20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1223,27 +1152,27 @@
           <t>IDS_PXSB103_FULL</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>修改</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">赫拉克勒斯 </t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">赫拉克勒斯 </t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Heracles</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Heracles</t>
         </is>
@@ -1258,11 +1187,7 @@
           <t>Heracles</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>赫拉克勒斯</t>
-        </is>
-      </c>
+      <c r="I21" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I21"/>
